--- a/SGC-CKN/Excel/0ad8039d-059c-47bb-8551-a12e7bea0dbb_Thanh_Hoá_P2-08_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/0ad8039d-059c-47bb-8551-a12e7bea0dbb_Thanh_Hoá_P2-08_D800_04-04-2026.xlsx
@@ -1364,16 +1364,16 @@
         <v>-26.3</v>
       </c>
       <c r="G17" s="25">
-        <v>-32.5</v>
+        <v>-39.5</v>
       </c>
       <c r="H17" s="25">
         <v>0.62</v>
       </c>
       <c r="I17" s="25">
-        <v>6.2</v>
+        <v>13.2</v>
       </c>
       <c r="J17" s="8">
-        <v>10.05</v>
+        <v>21.41</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
@@ -1396,19 +1396,19 @@
         <v>52</v>
       </c>
       <c r="F18" s="28">
-        <v>-32.5</v>
+        <v>-39.5</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.4</v>
+        <v>-44.46</v>
       </c>
       <c r="H18" s="28">
         <v>1.58</v>
       </c>
       <c r="I18" s="28">
-        <v>11.9</v>
-      </c>
-      <c r="J18" s="8">
-        <v>7.52</v>
+        <v>4.96</v>
+      </c>
+      <c r="J18" s="24">
+        <v>3.13</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>53</v>
@@ -1740,16 +1740,16 @@
         <v>-26.3</v>
       </c>
       <c r="F8" s="25">
-        <v>-32.5</v>
+        <v>-39.5</v>
       </c>
       <c r="G8" s="25">
         <v>0.62</v>
       </c>
       <c r="H8" s="25">
-        <v>6.2</v>
+        <v>13.2</v>
       </c>
       <c r="I8" s="8">
-        <v>10.05</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1766,19 +1766,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-32.5</v>
+        <v>-39.5</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.4</v>
+        <v>-44.46</v>
       </c>
       <c r="G9" s="28">
         <v>1.58</v>
       </c>
       <c r="H9" s="28">
-        <v>11.9</v>
-      </c>
-      <c r="I9" s="8">
-        <v>7.52</v>
+        <v>4.96</v>
+      </c>
+      <c r="I9" s="24">
+        <v>3.13</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,16 +1798,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-44.4</v>
+        <v>-44.46</v>
       </c>
       <c r="G10" s="33">
         <v>5.7</v>
       </c>
       <c r="H10" s="33">
-        <v>44.4</v>
+        <v>44.46</v>
       </c>
       <c r="I10" s="33">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
